--- a/Pemetaan_Roadmap_Penelitian_Sistem_Informasi.xlsx
+++ b/Pemetaan_Roadmap_Penelitian_Sistem_Informasi.xlsx
@@ -1112,7 +1112,7 @@
     <row r="31">
       <c r="A31" s="43" t="inlineStr">
         <is>
-          <t>Data SINTA ditarik 29 Agustus 2026 | Pemetaan disusun 29 Agustus 2026</t>
+          <t>Data SINTA ditarik 29 Agustus 2026 | Pemetaan disusun 30 Agustus 2026</t>
         </is>
       </c>
     </row>
